--- a/network_text.xlsx
+++ b/network_text.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://phgr.sharepoint.com/sites/50136/Freigegebene Dokumente/General/Dokumente/06 Atlasvorbereitung/netzwerk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD097D1A-84A1-466D-BDA4-4C35E5195035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B216D9E-D0BB-45EE-BA84-233A7719D747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-420" yWindow="288" windowWidth="21456" windowHeight="11796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,6 +44,7 @@
     <author>tc={C8A28836-8A0B-4145-9719-88700BEE571E}</author>
     <author>tc={AAA7F9E3-39A0-43F0-A0CB-7F57DA0BACD0}</author>
     <author>tc={E34BCF86-3571-459C-A67A-1A143E75D240}</author>
+    <author>tc={34E569D0-3C05-4F2B-A95F-675FCBF9FBEC}</author>
     <author>tc={B47C0599-C6FD-4C91-87C7-BB9A15CDD84B}</author>
     <author>tc={30C14E97-3C1F-43AC-8D4B-EB4FAE0132A7}</author>
     <author>tc={B4BB58FC-1FC3-4B58-AD17-CB5B8CA1F7D0}</author>
@@ -76,7 +77,15 @@
     «datier» ist auch in diesem Sinn üblich</t>
       </text>
     </comment>
-    <comment ref="C26" authorId="3" shapeId="0" xr:uid="{B47C0599-C6FD-4C91-87C7-BB9A15CDD84B}">
+    <comment ref="F21" authorId="3" shapeId="0" xr:uid="{34E569D0-3C05-4F2B-A95F-675FCBF9FBEC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Hier stand nur „dastrusch“, war das absicht?</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="4" shapeId="0" xr:uid="{B47C0599-C6FD-4C91-87C7-BB9A15CDD84B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -86,7 +95,7 @@
     Gut! Puter/Vallader verzeichnen nur recugnuscher ‘anerkennen’, das Wort ist aber auch im Gebrauch für ‘wiedererkennen’.</t>
       </text>
     </comment>
-    <comment ref="B27" authorId="4" shapeId="0" xr:uid="{30C14E97-3C1F-43AC-8D4B-EB4FAE0132A7}">
+    <comment ref="B27" authorId="5" shapeId="0" xr:uid="{30C14E97-3C1F-43AC-8D4B-EB4FAE0132A7}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -94,7 +103,7 @@
     Eher doch AngabE oder? Sonst versteht man noch, dass der Ort auch nicht gespeichert wird</t>
       </text>
     </comment>
-    <comment ref="C27" authorId="5" shapeId="0" xr:uid="{B4BB58FC-1FC3-4B58-AD17-CB5B8CA1F7D0}">
+    <comment ref="C27" authorId="6" shapeId="0" xr:uid="{B4BB58FC-1FC3-4B58-AD17-CB5B8CA1F7D0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -109,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="211">
   <si>
     <t>code</t>
   </si>
@@ -135,22 +144,22 @@
     <t>header</t>
   </si>
   <si>
-    <t>Zeichnen Sie Ihr soziales Netzwerk ein</t>
-  </si>
-  <si>
-    <t>Dessignei Vossa reit sociala</t>
+    <t>Visualisieren Sie Ihr soziales Netzwerk</t>
+  </si>
+  <si>
+    <t>Visualisei Vossa reit sociala</t>
   </si>
   <si>
     <t>Dissignead la Vossa reet soziala</t>
   </si>
   <si>
-    <t>Dessigne la Vossa reit sociala</t>
-  </si>
-  <si>
-    <t>Ch'Ella/El disegna Sia rait sociela</t>
-  </si>
-  <si>
-    <t>Ch'Ella/El disegna Sia rait sociala</t>
+    <t>Visualise la Vossa reit sociala</t>
+  </si>
+  <si>
+    <t>Ch'Ella/El visualisescha Sia rait sociela</t>
+  </si>
+  <si>
+    <t>Ch'Ella/El visualisescha Sia rait sociala</t>
   </si>
   <si>
     <t>language_header</t>
@@ -165,7 +174,7 @@
     <t>Quella parsùna bagliafa cun me ...</t>
   </si>
   <si>
-    <t>Chella persunga discorra cun me ...</t>
+    <t>Chella persunga discorra cun me …</t>
   </si>
   <si>
     <t>Quista persuna discuorra cun me ...</t>
@@ -177,10 +186,22 @@
     <t>instruction_contact</t>
   </si>
   <si>
-    <t>Nenne Personen, mit denen du mindestens 2 bis 3 mal pro Monat sprichst. Hinweis: gemeint sind alle mündlichen Formen der Interaktion (z. B. auch Telefongespräche u. ä.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numna persunas, cullas qualas ti discuorras silmeins 2 tochen 3 gadas </t>
+    <t>Nennen Sie Personen, mit denen Sie mindestens 2–3 mal pro Monat sprechen. Hinweis: gemeint sind alle mündlichen Formen der Interaktion (z. B. auch Telefongespräche)</t>
+  </si>
+  <si>
+    <t>Numnei persunas, cullas qualas Vus tschintscheis silmeins 2–3 gadas il meins. Tut las interacziuns a bucca ein relevontas (p.ex. era discuors al telefon).</t>
+  </si>
+  <si>
+    <t>Numnad parsùnas, cun las qualas Vus bagliafaz seglmains 2–3 geadas igl mains. Tut las interacziùns a buca en relevàntas (p.ex. ear dascurs agl telefon).</t>
+  </si>
+  <si>
+    <t>Numne persungas, cun las qualas Vous discurriz aglmanc 2–3 gedas agl meis. Tot las interacziuns a bucca èn relevantas (p.ex. er discurs agl telefon).</t>
+  </si>
+  <si>
+    <t>Ch'Ella/El nomna a persunas, cullas quelas Ella/El discuorra almain 2–3 voutas al mais. Tuot las interacziuns a buocha sun relevantas (p.ex. eir discuors al telefon).</t>
+  </si>
+  <si>
+    <t>Ch'Ella/El nomna a persunas, cullas qualas Ella/El discuorra almain 2–3 jadas al mais. Tuot las interacziuns a bocca sun relevantas (p.ex. eir discuors al telefon).</t>
   </si>
   <si>
     <t>monolingual_interaction</t>
@@ -216,7 +237,7 @@
     <t>my_idiom</t>
   </si>
   <si>
-    <t>Mein Idiom</t>
+    <t>mein Idiom</t>
   </si>
   <si>
     <t>sursilvan</t>
@@ -237,7 +258,7 @@
     <t>romansh</t>
   </si>
   <si>
-    <t>ein anders Idiom</t>
+    <t>ein anderes Idiom</t>
   </si>
   <si>
     <t>in auter idiom</t>
@@ -324,7 +345,7 @@
     <t>family_sector</t>
   </si>
   <si>
-    <t>Familie, Verwandschaft &amp; Partnerschaft</t>
+    <t>Familie, Verwandtschaft &amp; Partnerschaft</t>
   </si>
   <si>
     <t>famiglia, parentella &amp; partenari/a</t>
@@ -408,22 +429,22 @@
     <t>frequency_label</t>
   </si>
   <si>
-    <t>2 - 3 Mal pro Monat</t>
-  </si>
-  <si>
-    <t>2 - 3 gadas il meins</t>
-  </si>
-  <si>
-    <t>2 - 3 geadas igl mains</t>
-  </si>
-  <si>
-    <t>2 - 3 gedas agl meis</t>
-  </si>
-  <si>
-    <t>2 - 3 voutas al mais</t>
-  </si>
-  <si>
-    <t>2 - 3 jadas al mais</t>
+    <t>2–3 Mal pro Monat</t>
+  </si>
+  <si>
+    <t>2–3 gadas il meins</t>
+  </si>
+  <si>
+    <t>2–3 geadas igl mains</t>
+  </si>
+  <si>
+    <t>2–3 gedas agl meis</t>
+  </si>
+  <si>
+    <t>2–3 voutas al mais</t>
+  </si>
+  <si>
+    <t>2–3 jadas al mais</t>
   </si>
   <si>
     <t>location</t>
@@ -456,16 +477,16 @@
     <t>Con datier (emoziunalmein) sesentis Vus a quella persuna?</t>
   </si>
   <si>
-    <t>Quànt datier (emoziunalmeing) sasantez a quella parsùna?</t>
-  </si>
-  <si>
-    <t>Quant manevel ischas Vous emoziunalmaintg da chella persunga?</t>
-  </si>
-  <si>
-    <t>Quaunt dastrusch es Ella/El emoziunelmaing a quella persuna?</t>
-  </si>
-  <si>
-    <t>Quant dastrusch es El/Ella emoziunalmaing a quella persuna?</t>
+    <t>Quànt datier (emoziunalmeing) sasantez Vus a quella parsùna?</t>
+  </si>
+  <si>
+    <t>Quant manevel (emoziunalmaintg) az santiz Vous a chella persunga?</t>
+  </si>
+  <si>
+    <t>Quaunt dastrusch (emoziunalmaing) as sainta Ella/El a quista persuna?</t>
+  </si>
+  <si>
+    <t>Quant dastrusch (emoziunalmaing) as sainta Ella/El a quista persuna?</t>
   </si>
   <si>
     <t>not_very_close</t>
@@ -477,13 +498,13 @@
     <t>buca fetg datier</t>
   </si>
   <si>
-    <t>datier</t>
-  </si>
-  <si>
-    <t>manevel</t>
-  </si>
-  <si>
-    <t>dastrusch</t>
+    <t>betga fetg datier</t>
+  </si>
+  <si>
+    <t>betg fitg manevel</t>
+  </si>
+  <si>
+    <t>guera dastrusch</t>
   </si>
   <si>
     <t>somewhat_close</t>
@@ -495,13 +516,13 @@
     <t>in tec datier</t>
   </si>
   <si>
-    <t>pletost datier</t>
-  </si>
-  <si>
-    <t>pitost manevel</t>
-  </si>
-  <si>
-    <t>pütost dastrusch</t>
+    <t>egn tec datier</t>
+  </si>
+  <si>
+    <t>ampo manevel</t>
+  </si>
+  <si>
+    <t>ün pô dastrusch</t>
   </si>
   <si>
     <t>plüchöntsch dastrusch</t>
@@ -510,22 +531,16 @@
     <t>very_close</t>
   </si>
   <si>
-    <t>eher nahe</t>
-  </si>
-  <si>
-    <t>plitost distanziada/distanziaus</t>
-  </si>
-  <si>
-    <t>pletost distanztgeada/distanzgieu</t>
-  </si>
-  <si>
-    <t>pitost distanztgeda/distanztgea</t>
-  </si>
-  <si>
-    <t>pütost distanzieda/distanzio</t>
-  </si>
-  <si>
-    <t>plüchöntsch distanziada/distanzià</t>
+    <t>sehr nahe</t>
+  </si>
+  <si>
+    <t>fetg datier</t>
+  </si>
+  <si>
+    <t>fitg manevel</t>
+  </si>
+  <si>
+    <t>fich dastrusch</t>
   </si>
   <si>
     <t>extremely_close</t>
@@ -534,19 +549,13 @@
     <t>extrem nahe</t>
   </si>
   <si>
-    <t>distanziada/distanziaus</t>
-  </si>
-  <si>
-    <t>distanztgeada/distanzgieu</t>
-  </si>
-  <si>
-    <t>distanztgeda/distanztgea</t>
-  </si>
-  <si>
-    <t>distanzieda/distanzio</t>
-  </si>
-  <si>
-    <t>distanziada/distanzià</t>
+    <t>extrem datier</t>
+  </si>
+  <si>
+    <t>extrem manevel</t>
+  </si>
+  <si>
+    <t>extrem dastrusch</t>
   </si>
   <si>
     <t>describe_person</t>
@@ -699,19 +708,19 @@
     <t>Konnte nicht gespeichert werden:</t>
   </si>
   <si>
-    <t>Quei ha buca saviu vegnir segirau:</t>
-  </si>
-  <si>
-    <t>Quegl â betga savieu vagnir siro:</t>
-  </si>
-  <si>
-    <t>Chegl ò betg savia neir siero:</t>
-  </si>
-  <si>
-    <t>Que nun ho pudieu gnir sgüro:</t>
-  </si>
-  <si>
-    <t>Quai nun ha pudü gnir sgürà:</t>
+    <t>Igl ei buca stau pusseivel da segirar il suandont:</t>
+  </si>
+  <si>
+    <t>Igl e betga sto pussevel da sirar igl savundànt:</t>
+  </si>
+  <si>
+    <t>Igl è betg sto pussebel da sierar ilg suandont:</t>
+  </si>
+  <si>
+    <t>A nun es sto pussibel da sgürer il seguaint:</t>
+  </si>
+  <si>
+    <t>I nun es stat pussibel da sgürar il seguaint:</t>
   </si>
   <si>
     <t>cancel</t>
@@ -771,12 +780,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -791,13 +806,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1127,14 +1148,17 @@
   <threadedComment ref="B11" dT="2026-10-23T10:02:47.99" personId="{6A7B02D5-4886-498D-A831-D10CFD6826F3}" id="{AAA7F9E3-39A0-43F0-A0CB-7F57DA0BACD0}">
     <text>@Peter: Hier braucht es ein Feld für Freitext, damit die Teilnehmenden die Sprachen angeben können.</text>
   </threadedComment>
-  <threadedComment ref="C20" dT="2026-10-21T12:26:03.57" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{E34BCF86-3571-459C-A67A-1A143E75D240}">
+  <threadedComment ref="C20" dT="2026-10-21T12:26:03.57" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{E34BCF86-3571-459C-A67A-1A143E75D240}" done="1">
     <text>Das ist mal wörtlich übersetzt, wobei auf deutsch „nahe STEHEN“ glaub üblicher ist?
 Ich finde hier kein gutes Wort für „nahe“: „datier“ scheint mir zu physisch, „intim“ mit Konnotationen... vielleicht „proxim“?</text>
   </threadedComment>
   <threadedComment ref="C20" dT="2026-10-23T10:01:14.96" personId="{6A7B02D5-4886-498D-A831-D10CFD6826F3}" id="{3D5189F7-3F46-4A3B-A7DC-CD505BCB0F3E}" parentId="{E34BCF86-3571-459C-A67A-1A143E75D240}">
     <text>«datier» ist auch in diesem Sinn üblich</text>
   </threadedComment>
-  <threadedComment ref="C26" dT="2026-10-21T13:06:46.35" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{B47C0599-C6FD-4C91-87C7-BB9A15CDD84B}">
+  <threadedComment ref="F21" dT="2026-10-23T12:23:59.31" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{34E569D0-3C05-4F2B-A95F-675FCBF9FBEC}">
+    <text>Hier stand nur „dastrusch“, war das absicht?</text>
+  </threadedComment>
+  <threadedComment ref="C26" dT="2026-10-21T13:06:46.35" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{B47C0599-C6FD-4C91-87C7-BB9A15CDD84B}" done="1">
     <text>„wiedererkennen“ ist nur im Sursilvan und Surmiran im Dicziunari, die anderen Idiome hab ich mal analog gebildet...</text>
   </threadedComment>
   <threadedComment ref="C26" dT="2026-10-23T09:26:45.03" personId="{6A7B02D5-4886-498D-A831-D10CFD6826F3}" id="{A3B4F45D-4009-4C53-8EF1-21C862B55028}" parentId="{B47C0599-C6FD-4C91-87C7-BB9A15CDD84B}">
@@ -1143,7 +1167,7 @@
   <threadedComment ref="B27" dT="2026-10-21T12:58:00.80" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{30C14E97-3C1F-43AC-8D4B-EB4FAE0132A7}">
     <text>Eher doch AngabE oder? Sonst versteht man noch, dass der Ort auch nicht gespeichert wird</text>
   </threadedComment>
-  <threadedComment ref="C27" dT="2026-10-21T12:45:10.44" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{B4BB58FC-1FC3-4B58-AD17-CB5B8CA1F7D0}">
+  <threadedComment ref="C27" dT="2026-10-21T12:45:10.44" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{B4BB58FC-1FC3-4B58-AD17-CB5B8CA1F7D0}" done="1">
     <text>Thema „speichern“... hab jetzt mal Worttyp „segirar“ verwendet</text>
   </threadedComment>
   <threadedComment ref="C27" dT="2026-10-23T09:28:06.19" personId="{6A7B02D5-4886-498D-A831-D10CFD6826F3}" id="{194B4C83-F9D6-4411-BD60-C0AF7A294A8A}" parentId="{B4BB58FC-1FC3-4B58-AD17-CB5B8CA1F7D0}">
@@ -1155,7 +1179,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.85"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="40.42578125" style="1" customWidth="1"/>
@@ -1185,7 +1209,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="15">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1208,7 +1232,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1231,7 +1255,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="57.6">
+    <row r="4" spans="1:7" ht="73.7">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1241,462 +1265,474 @@
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="14.45" customHeight="1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="29.45">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>145</v>
@@ -1725,7 +1761,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="43.15">
+    <row r="26" spans="1:7" ht="44.25">
       <c r="A26" t="s">
         <v>152</v>
       </c>
@@ -1863,7 +1899,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" ht="29.45">
       <c r="A32" t="s">
         <v>194</v>
       </c>
@@ -1876,7 +1912,7 @@
       <c r="D32" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="4" t="s">
         <v>198</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -1940,6 +1976,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="7ca699bf-a106-4ec6-82ce-d27139ba879a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f0b9da4d-1c73-493c-b2df-f59844e8c1c6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100CEC7723783E6CF448061A208639A25CB" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="13737448da22da384c646477a5227b83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f0b9da4d-1c73-493c-b2df-f59844e8c1c6" xmlns:ns3="7ca699bf-a106-4ec6-82ce-d27139ba879a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8b20ac0a5a926328ecfe32515228de48" ns2:_="" ns3:_="">
     <xsd:import namespace="f0b9da4d-1c73-493c-b2df-f59844e8c1c6"/>
@@ -2140,28 +2196,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="7ca699bf-a106-4ec6-82ce-d27139ba879a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f0b9da4d-1c73-493c-b2df-f59844e8c1c6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB02FB40-69D8-4229-95A0-EB861B3F293A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA06F806-2292-4CF2-A4F8-5C72A634D22C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2169,5 +2205,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA06F806-2292-4CF2-A4F8-5C72A634D22C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8765FF1-6E80-488D-8A35-E349EA4CF688}"/>
 </file>
--- a/network_text.xlsx
+++ b/network_text.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://phgr.sharepoint.com/sites/50136/Freigegebene Dokumente/General/Dokumente/06 Atlasvorbereitung/netzwerk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B216D9E-D0BB-45EE-BA84-233A7719D747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFD0FA8A-17BC-44AC-9665-14421BF0E893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="504" windowWidth="22212" windowHeight="11796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,10 @@
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Hier stand nur „dastrusch“, war das absicht?</t>
+    Hier stand nur „dastrusch“, war das absicht?
+Reply:
+    Nein, das war ein Relikt der ursprünglichen Antwortreihe, die mit «nahe» begann 😉
+Buca fetg datier = Na fich dastrusch</t>
       </text>
     </comment>
     <comment ref="C26" authorId="4" shapeId="0" xr:uid="{B47C0599-C6FD-4C91-87C7-BB9A15CDD84B}">
@@ -150,7 +153,7 @@
     <t>Visualisei Vossa reit sociala</t>
   </si>
   <si>
-    <t>Dissignead la Vossa reet soziala</t>
+    <t>Visualisad la Vossa reet soziala</t>
   </si>
   <si>
     <t>Visualise la Vossa reit sociala</t>
@@ -504,7 +507,7 @@
     <t>betg fitg manevel</t>
   </si>
   <si>
-    <t>guera dastrusch</t>
+    <t>na fich dastrusch</t>
   </si>
   <si>
     <t>somewhat_close</t>
@@ -525,7 +528,7 @@
     <t>ün pô dastrusch</t>
   </si>
   <si>
-    <t>plüchöntsch dastrusch</t>
+    <t>ün pa dastrusch</t>
   </si>
   <si>
     <t>very_close</t>
@@ -780,18 +783,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -806,7 +803,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -816,9 +813,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1155,8 +1149,12 @@
   <threadedComment ref="C20" dT="2026-10-23T10:01:14.96" personId="{6A7B02D5-4886-498D-A831-D10CFD6826F3}" id="{3D5189F7-3F46-4A3B-A7DC-CD505BCB0F3E}" parentId="{E34BCF86-3571-459C-A67A-1A143E75D240}">
     <text>«datier» ist auch in diesem Sinn üblich</text>
   </threadedComment>
-  <threadedComment ref="F21" dT="2026-10-23T12:23:59.31" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{34E569D0-3C05-4F2B-A95F-675FCBF9FBEC}">
+  <threadedComment ref="F21" dT="2026-10-23T12:23:59.31" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{34E569D0-3C05-4F2B-A95F-675FCBF9FBEC}" done="1">
     <text>Hier stand nur „dastrusch“, war das absicht?</text>
+  </threadedComment>
+  <threadedComment ref="F21" dT="2026-10-23T14:39:19.33" personId="{6A7B02D5-4886-498D-A831-D10CFD6826F3}" id="{8638A529-9E5D-4AD4-86E8-5FDF5389B978}" parentId="{34E569D0-3C05-4F2B-A95F-675FCBF9FBEC}">
+    <text>Nein, das war ein Relikt der ursprünglichen Antwortreihe, die mit «nahe» begann 😉
+Buca fetg datier = Na fich dastrusch</text>
   </threadedComment>
   <threadedComment ref="C26" dT="2026-10-21T13:06:46.35" personId="{7A4393CE-17D0-40E4-AEB6-EB5BF76B1D80}" id="{B47C0599-C6FD-4C91-87C7-BB9A15CDD84B}" done="1">
     <text>„wiedererkennen“ ist nur im Sursilvan und Surmiran im Dicziunari, die anderen Idiome hab ich mal analog gebildet...</text>
@@ -1179,7 +1177,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.85"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="40.42578125" style="1" customWidth="1"/>
@@ -1209,7 +1207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1232,7 +1230,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1255,7 +1253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="73.7">
+    <row r="4" spans="1:7" ht="57.6">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1623,7 +1621,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="29.45">
+    <row r="20" spans="1:7" ht="28.9">
       <c r="A20" t="s">
         <v>116</v>
       </c>
@@ -1662,10 +1660,10 @@
       <c r="E21" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="1" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1761,7 +1759,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="44.25">
+    <row r="26" spans="1:7" ht="43.15">
       <c r="A26" t="s">
         <v>152</v>
       </c>
@@ -1899,7 +1897,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="29.45">
+    <row r="32" spans="1:7" ht="28.9">
       <c r="A32" t="s">
         <v>194</v>
       </c>
@@ -1987,15 +1985,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100CEC7723783E6CF448061A208639A25CB" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="13737448da22da384c646477a5227b83">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f0b9da4d-1c73-493c-b2df-f59844e8c1c6" xmlns:ns3="7ca699bf-a106-4ec6-82ce-d27139ba879a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8b20ac0a5a926328ecfe32515228de48" ns2:_="" ns3:_="">
     <xsd:import namespace="f0b9da4d-1c73-493c-b2df-f59844e8c1c6"/>
@@ -2196,14 +2185,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA06F806-2292-4CF2-A4F8-5C72A634D22C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D2A48D-B653-4230-8DAF-FF514CB9BBC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A14E44D1-BB1B-4B63-B214-8594CF0A04AD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8765FF1-6E80-488D-8A35-E349EA4CF688}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88D2A48D-B653-4230-8DAF-FF514CB9BBC6}"/>
 </file>